--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="104">
   <si>
     <t>#</t>
   </si>
@@ -324,6 +324,18 @@
   </si>
   <si>
     <t>Технология WebAssembly</t>
+  </si>
+  <si>
+    <t>Веб-платформа для интерактивного знакомства с методами предиктивного анализа</t>
+  </si>
+  <si>
+    <t>Веб-приложение для управления университетскими спортивными секциями «Campus Sport»</t>
+  </si>
+  <si>
+    <t>Веб-приложение для контроля заданий и сроков сдачи заданий для студентов</t>
+  </si>
+  <si>
+    <t>Веб-приложение для выявления мошеннически сообщений «ScamSeeker»</t>
   </si>
 </sst>
 </file>
@@ -451,7 +463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -490,6 +502,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -624,7 +637,7 @@
     <col min="5" max="5" width="39.88671875" customWidth="1"/>
     <col min="6" max="6" width="22.44140625" customWidth="1"/>
     <col min="7" max="7" width="22.88671875" customWidth="1"/>
-    <col min="8" max="8" width="22.44140625" customWidth="1"/>
+    <col min="8" max="8" width="90.5546875" customWidth="1"/>
     <col min="9" max="18" width="22.44140625" style="11" customWidth="1"/>
     <col min="19" max="19" width="33.21875" style="11" customWidth="1"/>
     <col min="20" max="20" width="28.6640625" style="11" customWidth="1"/>
@@ -728,760 +741,793 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D2">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G2">
         <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D3">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>93</v>
+      </c>
+      <c r="G3">
         <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-      <c r="E4" t="s">
-        <v>79</v>
-      </c>
       <c r="G4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>20</v>
-      </c>
-      <c r="B5" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
+      <c r="H5" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>8</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7">
         <v>3</v>
-      </c>
-      <c r="E7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G8">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
+        <v>1</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-      <c r="E10" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
+        <v>2</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11">
-        <v>5</v>
-      </c>
-      <c r="E11" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12">
-        <v>6</v>
-      </c>
-      <c r="E12" t="s">
-        <v>83</v>
-      </c>
       <c r="G12">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G13">
-        <v>9</v>
+        <v>5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>91</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+      <c r="H14" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>7</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G15">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="H15" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>37</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
+        <v>8</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="H16" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>26</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>10</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>6</v>
+      </c>
+      <c r="H17" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>27</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
+        <v>9</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>23</v>
-      </c>
-      <c r="B19" t="s">
-        <v>30</v>
+        <v>11</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>86</v>
+        <v>81</v>
+      </c>
+      <c r="G19">
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>39</v>
-      </c>
-      <c r="B20" t="s">
-        <v>46</v>
+        <v>7</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
+        <v>84</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A21" s="13">
-        <v>44</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="13">
-        <v>11</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-      <c r="Q21" s="14"/>
-      <c r="R21" s="14"/>
-      <c r="S21" s="14"/>
-      <c r="T21" s="14"/>
-      <c r="U21" s="14"/>
-      <c r="V21" s="14"/>
-      <c r="W21" s="14"/>
-      <c r="X21" s="14"/>
-      <c r="Y21" s="14"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="14"/>
-      <c r="AD21" s="14"/>
-      <c r="AE21" s="14"/>
+      <c r="A21">
+        <v>25</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21" t="s">
+        <v>82</v>
+      </c>
+      <c r="G21">
+        <v>8</v>
+      </c>
+      <c r="H21" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A22" s="13">
-        <v>45</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="13">
-        <v>11</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-      <c r="Q22" s="14"/>
-      <c r="R22" s="14"/>
-      <c r="S22" s="14"/>
-      <c r="T22" s="14"/>
-      <c r="U22" s="14"/>
-      <c r="V22" s="14"/>
-      <c r="W22" s="14"/>
-      <c r="X22" s="14"/>
-      <c r="Y22" s="14"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-      <c r="AB22" s="14"/>
-      <c r="AC22" s="14"/>
-      <c r="AD22" s="14"/>
-      <c r="AE22" s="14"/>
+      <c r="A22">
+        <v>33</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22">
+        <v>8</v>
+      </c>
+      <c r="H22" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="H23" t="s">
+        <v>103</v>
+      </c>
+      <c r="AD23" s="11" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D24">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E24" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G24">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D25">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G25">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G26">
-        <v>8</v>
-      </c>
-      <c r="AD26" s="11" t="s">
-        <v>97</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s">
-        <v>35</v>
+        <v>19</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D27">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>14</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D29">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>93</v>
-      </c>
-      <c r="G29">
-        <v>1</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>3</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
+        <v>39</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D30">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>6</v>
-      </c>
-      <c r="B31" s="1" t="s">
+      <c r="A31" s="13">
+        <v>44</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" s="13">
         <v>11</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31">
-        <v>16</v>
-      </c>
-      <c r="E31" t="s">
-        <v>94</v>
-      </c>
+      <c r="E31" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="14"/>
+      <c r="AE31" s="14"/>
     </row>
     <row r="32" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>43</v>
-      </c>
-      <c r="B32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D32">
-        <v>17</v>
-      </c>
-      <c r="E32" t="s">
-        <v>95</v>
-      </c>
+      <c r="A32" s="13">
+        <v>45</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" s="13">
+        <v>11</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="14"/>
+      <c r="AA32" s="14"/>
+      <c r="AB32" s="14"/>
+      <c r="AC32" s="14"/>
+      <c r="AD32" s="14"/>
+      <c r="AE32" s="14"/>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A33" s="13">
-        <v>46</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13">
-        <v>18</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14"/>
-      <c r="S33" s="14"/>
-      <c r="T33" s="14"/>
-      <c r="U33" s="14"/>
-      <c r="V33" s="14"/>
-      <c r="W33" s="14"/>
-      <c r="X33" s="14"/>
-      <c r="Y33" s="14"/>
-      <c r="Z33" s="14"/>
-      <c r="AA33" s="14"/>
-      <c r="AB33" s="14"/>
-      <c r="AC33" s="14"/>
-      <c r="AD33" s="14"/>
-      <c r="AE33" s="14"/>
+      <c r="A33">
+        <v>28</v>
+      </c>
+      <c r="B33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33">
+        <v>14</v>
+      </c>
+      <c r="E33" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G34">
-        <v>4</v>
+      <c r="D34">
+        <v>16</v>
+      </c>
+      <c r="E34" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G35">
-        <v>4</v>
+      <c r="D35">
+        <v>16</v>
+      </c>
+      <c r="E35" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>5</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>10</v>
+        <v>43</v>
+      </c>
+      <c r="B36" t="s">
+        <v>50</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="D36">
+        <v>17</v>
+      </c>
+      <c r="E36" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>12</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="1" t="s">
+      <c r="A37" s="13">
+        <v>46</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13">
         <v>18</v>
       </c>
+      <c r="E37" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14"/>
+      <c r="R37" s="14"/>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
+      <c r="Y37" s="14"/>
+      <c r="Z37" s="14"/>
+      <c r="AA37" s="14"/>
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="14"/>
+      <c r="AD37" s="14"/>
+      <c r="AE37" s="14"/>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G38">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39">
+        <v>12</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>18</v>
@@ -1489,10 +1535,10 @@
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>18</v>
@@ -1500,21 +1546,21 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>24</v>
-      </c>
-      <c r="B41" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -1522,10 +1568,10 @@
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -1533,16 +1579,13 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="G44">
-        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.25">
@@ -1665,7 +1708,7 @@
   </sheetData>
   <autoFilter ref="A1:AE1">
     <sortState ref="A2:AE47">
-      <sortCondition ref="D1"/>
+      <sortCondition ref="G1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.0249999999999999" bottom="1.0249999999999999" header="0.78749999999999998" footer="0.78749999999999998"/>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -14,7 +14,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ИТ_5!$A$1:$AE$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Очерёдность выступлений'!$A$1:$L$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="108">
   <si>
     <t>#</t>
   </si>
@@ -182,9 +182,6 @@
     <t>Оценка презентации</t>
   </si>
   <si>
-    <t>Видение проекта</t>
-  </si>
-  <si>
     <t>Бизнес-процессы</t>
   </si>
   <si>
@@ -336,6 +333,21 @@
   </si>
   <si>
     <t>Веб-приложение для выявления мошеннически сообщений «ScamSeeker»</t>
+  </si>
+  <si>
+    <t>Платформа для поиска мероприятий и единомышленников для студентов «Abstracteam»</t>
+  </si>
+  <si>
+    <t>Веб-приложение для создания заказа у службы кейтеринга “GastroHub”</t>
+  </si>
+  <si>
+    <t>платформа с онлайн курсами</t>
+  </si>
+  <si>
+    <t>Онлайн-платформа для создания и запуска мультиагентных систем "ModelLab"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Видение проекта </t>
   </si>
 </sst>
 </file>
@@ -346,7 +358,7 @@
     <numFmt numFmtId="164" formatCode="dd\.mm"/>
     <numFmt numFmtId="165" formatCode="d\.m"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -381,6 +393,14 @@
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="7">
@@ -463,19 +483,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -489,9 +503,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -503,6 +514,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -638,105 +673,106 @@
     <col min="6" max="6" width="22.44140625" customWidth="1"/>
     <col min="7" max="7" width="22.88671875" customWidth="1"/>
     <col min="8" max="8" width="90.5546875" customWidth="1"/>
-    <col min="9" max="18" width="22.44140625" style="11" customWidth="1"/>
-    <col min="19" max="19" width="33.21875" style="11" customWidth="1"/>
-    <col min="20" max="20" width="28.6640625" style="11" customWidth="1"/>
-    <col min="21" max="31" width="22.44140625" style="11" customWidth="1"/>
+    <col min="9" max="9" width="20.44140625" style="17" customWidth="1"/>
+    <col min="10" max="18" width="22.44140625" style="17" customWidth="1"/>
+    <col min="19" max="19" width="33.21875" style="17" customWidth="1"/>
+    <col min="20" max="20" width="28.6640625" style="17" customWidth="1"/>
+    <col min="21" max="31" width="22.44140625" style="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:31" s="21" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="20" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="20" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="Z1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AA1" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="16" t="s">
         <v>73</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -753,10 +789,25 @@
         <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G2">
         <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -773,24 +824,60 @@
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
+      <c r="H3" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J3" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>77</v>
+      </c>
       <c r="G4">
         <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L4" s="17" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
@@ -807,13 +894,25 @@
         <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G5">
         <v>2</v>
       </c>
-      <c r="H5" s="16" t="s">
-        <v>100</v>
+      <c r="H5" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
@@ -830,13 +929,25 @@
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
-      <c r="H6" s="16" t="s">
-        <v>100</v>
+      <c r="H6" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
@@ -853,10 +964,25 @@
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G7">
         <v>3</v>
+      </c>
+      <c r="H7" t="s">
+        <v>103</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
@@ -873,10 +999,25 @@
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G8">
         <v>3</v>
+      </c>
+      <c r="H8" t="s">
+        <v>103</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L8" s="17" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
@@ -893,10 +1034,25 @@
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G9">
         <v>3</v>
+      </c>
+      <c r="H9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
@@ -943,48 +1099,72 @@
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E14" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G14">
         <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
@@ -1001,13 +1181,25 @@
         <v>13</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15" t="s">
-        <v>101</v>
+        <v>100</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="17" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
@@ -1024,16 +1216,28 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G16">
         <v>6</v>
       </c>
       <c r="H16" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>10</v>
       </c>
@@ -1047,41 +1251,68 @@
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G17">
         <v>6</v>
       </c>
       <c r="H17" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L17" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G18">
         <v>7</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L18" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>6</v>
@@ -1090,61 +1321,106 @@
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G19">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
+        <v>104</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L19" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E20" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="G20">
         <v>7</v>
       </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="H20" t="s">
+        <v>104</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L20" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D21">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E21" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="G21">
         <v>8</v>
       </c>
       <c r="H21" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="AD21" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -1153,67 +1429,82 @@
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G22">
         <v>8</v>
       </c>
       <c r="H22" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L22" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D23">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G23">
         <v>8</v>
       </c>
       <c r="H23" t="s">
-        <v>103</v>
-      </c>
-      <c r="AD23" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="I23" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" s="17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D24">
-        <v>6</v>
-      </c>
-      <c r="E24" t="s">
-        <v>83</v>
       </c>
       <c r="G24">
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -1222,356 +1513,268 @@
         <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G25">
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E26" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G26">
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27">
+        <v>16</v>
+      </c>
+      <c r="E27" t="s">
+        <v>93</v>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>6</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28">
+        <v>16</v>
+      </c>
+      <c r="E28" t="s">
+        <v>93</v>
+      </c>
+      <c r="G28">
+        <v>10</v>
+      </c>
+      <c r="H28" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>4</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>5</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>12</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>4</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D28">
-        <v>7</v>
-      </c>
-      <c r="E28" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>23</v>
-      </c>
-      <c r="B29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29">
-        <v>10</v>
-      </c>
-      <c r="E29" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>39</v>
-      </c>
-      <c r="B30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30">
-        <v>10</v>
-      </c>
-      <c r="E30" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A31" s="13">
-        <v>44</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31" s="13">
-        <v>11</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="14"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="14"/>
-      <c r="Q31" s="14"/>
-      <c r="R31" s="14"/>
-      <c r="S31" s="14"/>
-      <c r="T31" s="14"/>
-      <c r="U31" s="14"/>
-      <c r="V31" s="14"/>
-      <c r="W31" s="14"/>
-      <c r="X31" s="14"/>
-      <c r="Y31" s="14"/>
-      <c r="Z31" s="14"/>
-      <c r="AA31" s="14"/>
-      <c r="AB31" s="14"/>
-      <c r="AC31" s="14"/>
-      <c r="AD31" s="14"/>
-      <c r="AE31" s="14"/>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A32" s="13">
-        <v>45</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D32" s="13">
-        <v>11</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14"/>
-      <c r="S32" s="14"/>
-      <c r="T32" s="14"/>
-      <c r="U32" s="14"/>
-      <c r="V32" s="14"/>
-      <c r="W32" s="14"/>
-      <c r="X32" s="14"/>
-      <c r="Y32" s="14"/>
-      <c r="Z32" s="14"/>
-      <c r="AA32" s="14"/>
-      <c r="AB32" s="14"/>
-      <c r="AC32" s="14"/>
-      <c r="AD32" s="14"/>
-      <c r="AE32" s="14"/>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>15</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>28</v>
-      </c>
-      <c r="B33" t="s">
-        <v>35</v>
+        <v>17</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33">
-        <v>14</v>
-      </c>
-      <c r="E33" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D34">
-        <v>16</v>
-      </c>
-      <c r="E34" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>6</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
+      </c>
+      <c r="B35" t="s">
+        <v>30</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D35">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E35" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B36" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D36">
-        <v>17</v>
-      </c>
-      <c r="E36" t="s">
-        <v>95</v>
-      </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A37" s="13">
-        <v>46</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13">
-        <v>18</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
-      <c r="Q37" s="14"/>
-      <c r="R37" s="14"/>
-      <c r="S37" s="14"/>
-      <c r="T37" s="14"/>
-      <c r="U37" s="14"/>
-      <c r="V37" s="14"/>
-      <c r="W37" s="14"/>
-      <c r="X37" s="14"/>
-      <c r="Y37" s="14"/>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="14"/>
-      <c r="AC37" s="14"/>
-      <c r="AD37" s="14"/>
-      <c r="AE37" s="14"/>
+      <c r="A37">
+        <v>28</v>
+      </c>
+      <c r="B37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37">
+        <v>14</v>
+      </c>
+      <c r="E37" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>5</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="B38" t="s">
+        <v>36</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>12</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="B39" t="s">
+        <v>37</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>17</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="B40" t="s">
+        <v>41</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>21</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>27</v>
+        <v>36</v>
+      </c>
+      <c r="B41" t="s">
+        <v>43</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D41">
+        <v>12</v>
+      </c>
+      <c r="E41" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -1579,131 +1782,137 @@
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="45" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>34</v>
-      </c>
-      <c r="B45" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45"/>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="11"/>
-      <c r="Q45" s="11"/>
-      <c r="R45" s="11"/>
-      <c r="S45" s="11"/>
-      <c r="T45" s="11"/>
-      <c r="U45" s="11"/>
-      <c r="V45" s="11"/>
-      <c r="W45" s="11"/>
-      <c r="X45" s="11"/>
-      <c r="Y45" s="11"/>
-      <c r="Z45" s="11"/>
-      <c r="AA45" s="11"/>
-      <c r="AB45" s="11"/>
-      <c r="AC45" s="11"/>
-      <c r="AD45" s="11"/>
-      <c r="AE45" s="11"/>
-    </row>
-    <row r="46" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>35</v>
-      </c>
-      <c r="B46" t="s">
-        <v>42</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46"/>
-      <c r="G46"/>
-      <c r="H46"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11"/>
-      <c r="Q46" s="11"/>
-      <c r="R46" s="11"/>
-      <c r="S46" s="11"/>
-      <c r="T46" s="11"/>
-      <c r="U46" s="11"/>
-      <c r="V46" s="11"/>
-      <c r="W46" s="11"/>
-      <c r="X46" s="11"/>
-      <c r="Y46" s="11"/>
-      <c r="Z46" s="11"/>
-      <c r="AA46" s="11"/>
-      <c r="AB46" s="11"/>
-      <c r="AC46" s="11"/>
-      <c r="AD46" s="11"/>
-      <c r="AE46" s="11"/>
-    </row>
-    <row r="47" spans="1:31" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>41</v>
-      </c>
-      <c r="B47" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D47"/>
-      <c r="E47"/>
-      <c r="F47"/>
-      <c r="G47"/>
-      <c r="H47"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="11"/>
-      <c r="P47" s="11"/>
-      <c r="Q47" s="11"/>
-      <c r="R47" s="11"/>
-      <c r="S47" s="11"/>
-      <c r="T47" s="11"/>
-      <c r="U47" s="11"/>
-      <c r="V47" s="11"/>
-      <c r="W47" s="11"/>
-      <c r="X47" s="11"/>
-      <c r="Y47" s="11"/>
-      <c r="Z47" s="11"/>
-      <c r="AA47" s="11"/>
-      <c r="AB47" s="11"/>
-      <c r="AC47" s="11"/>
-      <c r="AD47" s="11"/>
-      <c r="AE47" s="11"/>
+      <c r="D44">
+        <v>17</v>
+      </c>
+      <c r="E44" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="10">
+        <v>44</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="10">
+        <v>11</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+      <c r="L45" s="18"/>
+      <c r="M45" s="18"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="18"/>
+      <c r="R45" s="18"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="18"/>
+      <c r="V45" s="18"/>
+      <c r="W45" s="18"/>
+      <c r="X45" s="18"/>
+      <c r="Y45" s="18"/>
+      <c r="Z45" s="18"/>
+      <c r="AA45" s="18"/>
+      <c r="AB45" s="18"/>
+      <c r="AC45" s="18"/>
+      <c r="AD45" s="18"/>
+      <c r="AE45" s="18"/>
+    </row>
+    <row r="46" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="10">
+        <v>45</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" s="10">
+        <v>11</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="18"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="18"/>
+      <c r="R46" s="18"/>
+      <c r="S46" s="18"/>
+      <c r="T46" s="18"/>
+      <c r="U46" s="18"/>
+      <c r="V46" s="18"/>
+      <c r="W46" s="18"/>
+      <c r="X46" s="18"/>
+      <c r="Y46" s="18"/>
+      <c r="Z46" s="18"/>
+      <c r="AA46" s="18"/>
+      <c r="AB46" s="18"/>
+      <c r="AC46" s="18"/>
+      <c r="AD46" s="18"/>
+      <c r="AE46" s="18"/>
+    </row>
+    <row r="47" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="10">
+        <v>46</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="10">
+        <v>18</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="I47" s="18"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="18"/>
+      <c r="M47" s="18"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="18"/>
+      <c r="R47" s="18"/>
+      <c r="S47" s="18"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="18"/>
+      <c r="V47" s="18"/>
+      <c r="W47" s="18"/>
+      <c r="X47" s="18"/>
+      <c r="Y47" s="18"/>
+      <c r="Z47" s="18"/>
+      <c r="AA47" s="18"/>
+      <c r="AB47" s="18"/>
+      <c r="AC47" s="18"/>
+      <c r="AD47" s="18"/>
+      <c r="AE47" s="18"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AE1">
@@ -1730,29 +1939,29 @@
     <col min="3" max="3" width="14.109375" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
     <col min="5" max="5" width="39.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" style="12" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" style="12" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" style="12" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" style="12" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" style="12" customWidth="1"/>
-    <col min="11" max="11" width="15" style="12" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" style="12" customWidth="1"/>
-    <col min="13" max="13" width="28.33203125" style="9" customWidth="1"/>
-    <col min="14" max="14" width="20.109375" style="9" customWidth="1"/>
-    <col min="15" max="15" width="17.109375" style="9" customWidth="1"/>
-    <col min="16" max="16" width="23.21875" style="9" customWidth="1"/>
-    <col min="17" max="17" width="20.33203125" style="9" customWidth="1"/>
-    <col min="18" max="18" width="18.109375" style="9" customWidth="1"/>
-    <col min="19" max="19" width="35.6640625" style="9" customWidth="1"/>
-    <col min="20" max="20" width="36.88671875" style="9" customWidth="1"/>
-    <col min="21" max="21" width="17.33203125" style="9" customWidth="1"/>
-    <col min="22" max="22" width="18.21875" style="9" customWidth="1"/>
-    <col min="23" max="23" width="18.33203125" style="9" customWidth="1"/>
-    <col min="24" max="24" width="21.109375" style="9" customWidth="1"/>
-    <col min="25" max="25" width="19.109375" style="9" customWidth="1"/>
-    <col min="26" max="26" width="21.33203125" style="9" customWidth="1"/>
-    <col min="27" max="27" width="19.21875" style="9" customWidth="1"/>
-    <col min="28" max="16384" width="12.6640625" style="9"/>
+    <col min="6" max="6" width="14.109375" style="9" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="9" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" style="9" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" style="9" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" style="9" customWidth="1"/>
+    <col min="11" max="11" width="15" style="9" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" style="9" customWidth="1"/>
+    <col min="13" max="13" width="28.33203125" style="7" customWidth="1"/>
+    <col min="14" max="14" width="20.109375" style="7" customWidth="1"/>
+    <col min="15" max="15" width="17.109375" style="7" customWidth="1"/>
+    <col min="16" max="16" width="23.21875" style="7" customWidth="1"/>
+    <col min="17" max="17" width="20.33203125" style="7" customWidth="1"/>
+    <col min="18" max="18" width="18.109375" style="7" customWidth="1"/>
+    <col min="19" max="19" width="35.6640625" style="7" customWidth="1"/>
+    <col min="20" max="20" width="36.88671875" style="7" customWidth="1"/>
+    <col min="21" max="21" width="17.33203125" style="7" customWidth="1"/>
+    <col min="22" max="22" width="18.21875" style="7" customWidth="1"/>
+    <col min="23" max="23" width="18.33203125" style="7" customWidth="1"/>
+    <col min="24" max="24" width="21.109375" style="7" customWidth="1"/>
+    <col min="25" max="25" width="19.109375" style="7" customWidth="1"/>
+    <col min="26" max="26" width="21.33203125" style="7" customWidth="1"/>
+    <col min="27" max="27" width="19.21875" style="7" customWidth="1"/>
+    <col min="28" max="16384" width="12.6640625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
@@ -1769,768 +1978,725 @@
         <v>4</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F1" s="6">
+        <v>74</v>
+      </c>
+      <c r="F1" s="4">
         <v>46298</v>
       </c>
-      <c r="G1" s="7">
+      <c r="G1" s="5">
         <v>46312</v>
       </c>
-      <c r="H1" s="7">
+      <c r="H1" s="5">
         <v>46326</v>
       </c>
-      <c r="I1" s="7">
+      <c r="I1" s="5">
         <v>46340</v>
       </c>
-      <c r="J1" s="7">
+      <c r="J1" s="5">
         <v>46354</v>
       </c>
-      <c r="K1" s="7">
+      <c r="K1" s="5">
         <v>46368</v>
       </c>
-      <c r="L1" s="8" t="s">
-        <v>77</v>
+      <c r="L1" s="6" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="12">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="12">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="12">
-        <v>1</v>
+        <v>93</v>
+      </c>
+      <c r="H4" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>83</v>
+      </c>
+      <c r="I5" s="9">
         <v>2</v>
-      </c>
-      <c r="E5" t="s">
-        <v>79</v>
-      </c>
-      <c r="H5" s="12">
-        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" s="15">
-        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
-      </c>
-      <c r="H7" s="15">
-        <v>3</v>
+        <v>93</v>
+      </c>
+      <c r="H7" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="15">
+        <v>83</v>
+      </c>
+      <c r="I8" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H9" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>25</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="12">
+        <v>80</v>
+      </c>
+      <c r="H10" s="12">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="12">
-        <v>2</v>
+        <v>79</v>
+      </c>
+      <c r="H11" s="12">
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>40</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="D12">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>83</v>
-      </c>
-      <c r="I12" s="12">
-        <v>1</v>
+        <v>80</v>
+      </c>
+      <c r="H12" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>42</v>
-      </c>
-      <c r="B13" t="s">
-        <v>49</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13">
-        <v>6</v>
-      </c>
-      <c r="E13" t="s">
-        <v>83</v>
-      </c>
-      <c r="I13" s="12">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
-      </c>
-      <c r="I14" s="12">
-        <v>2</v>
+        <v>92</v>
+      </c>
+      <c r="H14" s="9">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
-      </c>
-      <c r="I15" s="12">
-        <v>2</v>
+        <v>92</v>
+      </c>
+      <c r="H15" s="9">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>37</v>
-      </c>
-      <c r="B16" t="s">
-        <v>44</v>
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16">
-        <v>8</v>
-      </c>
-      <c r="E16" t="s">
-        <v>85</v>
-      </c>
-      <c r="I16" s="12">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>26</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" s="12">
-        <v>4</v>
+        <v>77</v>
+      </c>
+      <c r="G17" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>27</v>
-      </c>
-      <c r="B18" t="s">
-        <v>34</v>
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18">
-        <v>9</v>
-      </c>
-      <c r="E18" t="s">
-        <v>89</v>
-      </c>
-      <c r="I18" s="12">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>23</v>
-      </c>
-      <c r="B19" t="s">
-        <v>30</v>
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>86</v>
-      </c>
-      <c r="G19" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" s="10" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="H19" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="8" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>39</v>
-      </c>
-      <c r="B20" t="s">
-        <v>46</v>
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>86</v>
-      </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12">
-        <v>3</v>
-      </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="14"/>
+        <v>77</v>
+      </c>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9">
+        <v>1</v>
+      </c>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="11"/>
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1">
-        <v>44</v>
+      <c r="A21">
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D21" s="1">
-        <v>11</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J21" s="12">
+        <v>18</v>
+      </c>
+      <c r="D21">
+        <v>2</v>
+      </c>
+      <c r="E21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1">
-        <v>45</v>
+      <c r="A22">
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" s="1">
-        <v>11</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J22" s="12">
-        <v>1</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D23">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E23" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="12">
-        <v>4</v>
+        <v>91</v>
+      </c>
+      <c r="I23" s="9">
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D24">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E24" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="12">
-        <v>4</v>
+        <v>85</v>
+      </c>
+      <c r="G24" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D25">
-        <v>13</v>
-      </c>
-      <c r="E25" t="s">
-        <v>91</v>
-      </c>
-      <c r="H25" s="12">
-        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E26" t="s">
-        <v>92</v>
-      </c>
-      <c r="I26" s="12">
-        <v>5</v>
+        <v>81</v>
+      </c>
+      <c r="G26" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D27">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>92</v>
-      </c>
-      <c r="I27" s="12">
-        <v>5</v>
+        <v>88</v>
+      </c>
+      <c r="I27" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>13</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D28">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>93</v>
-      </c>
-      <c r="H28" s="12">
-        <v>5</v>
+        <v>88</v>
+      </c>
+      <c r="I28" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D29">
         <v>14</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29">
-        <v>15</v>
-      </c>
       <c r="E29" t="s">
-        <v>93</v>
-      </c>
-      <c r="H29" s="12">
+        <v>91</v>
+      </c>
+      <c r="I29" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>3</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D30">
-        <v>16</v>
-      </c>
-      <c r="E30" t="s">
-        <v>94</v>
-      </c>
-      <c r="H30" s="12">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>6</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>11</v>
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D31">
-        <v>16</v>
-      </c>
-      <c r="E31" t="s">
-        <v>94</v>
-      </c>
-      <c r="H31" s="12">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D32">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E32" t="s">
-        <v>95</v>
-      </c>
-      <c r="I32" s="12">
-        <v>6</v>
+        <v>90</v>
+      </c>
+      <c r="H32" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
-        <v>46</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1">
-        <v>18</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J33" s="12">
-        <v>2</v>
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>1</v>
-      </c>
-      <c r="B34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34">
         <v>5</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>6</v>
+      <c r="E34" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>2</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>5</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="37" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37">
         <v>12</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>18</v>
+      <c r="E37" t="s">
+        <v>89</v>
+      </c>
+      <c r="G37" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>15</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D38">
+        <v>8</v>
+      </c>
+      <c r="E38" t="s">
+        <v>84</v>
+      </c>
+      <c r="I38" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>17</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D39">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>90</v>
+      </c>
+      <c r="H39" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>21</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>27</v>
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>18</v>
+        <v>29</v>
+      </c>
+      <c r="D40">
+        <v>10</v>
+      </c>
+      <c r="E40" t="s">
+        <v>85</v>
+      </c>
+      <c r="G40" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
+      <c r="E41" t="s">
+        <v>82</v>
+      </c>
+      <c r="I41" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -2538,100 +2704,136 @@
     </row>
     <row r="43" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D43">
+        <v>6</v>
+      </c>
+      <c r="E43" t="s">
+        <v>82</v>
+      </c>
+      <c r="I43" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
       </c>
+      <c r="D44">
+        <v>17</v>
+      </c>
+      <c r="E44" t="s">
+        <v>94</v>
+      </c>
+      <c r="I44" s="9">
+        <v>6</v>
+      </c>
     </row>
     <row r="45" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>34</v>
-      </c>
-      <c r="B45" t="s">
-        <v>41</v>
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
+      </c>
+      <c r="D45" s="1">
+        <v>11</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="J45" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:31" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>35</v>
-      </c>
-      <c r="B46" t="s">
-        <v>42</v>
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D46"/>
-      <c r="E46"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="12"/>
-      <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
+        <v>6</v>
+      </c>
+      <c r="D46" s="1">
+        <v>11</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9">
+        <v>1</v>
+      </c>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
     </row>
     <row r="47" spans="1:31" s="1" customFormat="1" ht="13.2" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>41</v>
-      </c>
-      <c r="B47" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D47"/>
-      <c r="E47"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="12"/>
-      <c r="J47" s="12"/>
-      <c r="K47" s="12"/>
-      <c r="L47" s="12"/>
-      <c r="M47" s="12"/>
-      <c r="N47" s="12"/>
-      <c r="O47" s="12"/>
-      <c r="P47" s="12"/>
-      <c r="Q47" s="12"/>
-      <c r="R47" s="12"/>
-      <c r="S47" s="12"/>
-      <c r="T47" s="12"/>
-      <c r="U47" s="12"/>
-      <c r="V47" s="12"/>
-      <c r="W47" s="12"/>
-      <c r="X47" s="12"/>
-      <c r="Y47" s="12"/>
-      <c r="Z47" s="12"/>
-      <c r="AA47" s="12"/>
-      <c r="AB47" s="12"/>
-      <c r="AC47" s="12"/>
-      <c r="AD47" s="12"/>
-      <c r="AE47" s="12"/>
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="1">
+        <v>18</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9">
+        <v>2</v>
+      </c>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+      <c r="M47" s="9"/>
+      <c r="N47" s="9"/>
+      <c r="O47" s="9"/>
+      <c r="P47" s="9"/>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9"/>
+      <c r="V47" s="9"/>
+      <c r="W47" s="9"/>
+      <c r="X47" s="9"/>
+      <c r="Y47" s="9"/>
+      <c r="Z47" s="9"/>
+      <c r="AA47" s="9"/>
+      <c r="AB47" s="9"/>
+      <c r="AC47" s="9"/>
+      <c r="AD47" s="9"/>
+      <c r="AE47" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1">
     <sortState ref="A2:K47">
-      <sortCondition ref="D1"/>
+      <sortCondition ref="A1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="109">
   <si>
     <t>#</t>
   </si>
@@ -341,13 +341,16 @@
     <t>Веб-приложение для создания заказа у службы кейтеринга “GastroHub”</t>
   </si>
   <si>
-    <t>платформа с онлайн курсами</t>
-  </si>
-  <si>
     <t>Онлайн-платформа для создания и запуска мультиагентных систем "ModelLab"</t>
   </si>
   <si>
     <t xml:space="preserve">Видение проекта </t>
+  </si>
+  <si>
+    <t>Мой список покупок</t>
+  </si>
+  <si>
+    <t>Платформа с онлайн курсами</t>
   </si>
 </sst>
 </file>
@@ -706,7 +709,7 @@
         <v>75</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>52</v>
@@ -795,7 +798,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I2" s="17" t="s">
         <v>96</v>
@@ -830,7 +833,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I3" s="17" t="s">
         <v>96</v>
@@ -865,7 +868,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>96</v>
@@ -1237,7 +1240,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>10</v>
       </c>
@@ -1272,7 +1275,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>7</v>
       </c>
@@ -1307,7 +1310,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>9</v>
       </c>
@@ -1342,7 +1345,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>11</v>
       </c>
@@ -1377,7 +1380,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>22</v>
       </c>
@@ -1415,7 +1418,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>25</v>
       </c>
@@ -1450,7 +1453,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>33</v>
       </c>
@@ -1485,7 +1488,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>35</v>
       </c>
@@ -1499,7 +1502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>40</v>
       </c>
@@ -1519,7 +1522,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>42</v>
       </c>
@@ -1539,7 +1542,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>3</v>
       </c>
@@ -1559,10 +1562,10 @@
         <v>10</v>
       </c>
       <c r="H27" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>6</v>
       </c>
@@ -1582,65 +1585,137 @@
         <v>10</v>
       </c>
       <c r="H28" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A29">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A29" s="10">
+        <v>44</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" s="10">
+        <v>11</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10">
+        <v>11</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" s="18"/>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18"/>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="18"/>
+      <c r="R29" s="18"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="18"/>
+      <c r="V29" s="18"/>
+      <c r="W29" s="18"/>
+      <c r="X29" s="18"/>
+      <c r="Y29" s="18"/>
+      <c r="Z29" s="18"/>
+      <c r="AA29" s="18"/>
+      <c r="AB29" s="18"/>
+      <c r="AC29" s="18"/>
+      <c r="AD29" s="18"/>
+      <c r="AE29" s="18"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A30" s="10">
+        <v>45</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" s="10">
+        <v>11</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10">
+        <v>11</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="Q30" s="18"/>
+      <c r="R30" s="18"/>
+      <c r="S30" s="18"/>
+      <c r="T30" s="18"/>
+      <c r="U30" s="18"/>
+      <c r="V30" s="18"/>
+      <c r="W30" s="18"/>
+      <c r="X30" s="18"/>
+      <c r="Y30" s="18"/>
+      <c r="Z30" s="18"/>
+      <c r="AA30" s="18"/>
+      <c r="AB30" s="18"/>
+      <c r="AC30" s="18"/>
+      <c r="AD30" s="18"/>
+      <c r="AE30" s="18"/>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>4</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B31" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D29">
+      <c r="C31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31">
         <v>7</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E31" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A30">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>5</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>12</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>15</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="C32" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33">
+        <v>12</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>18</v>
@@ -1648,10 +1723,10 @@
     </row>
     <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34">
+        <v>15</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>18</v>
@@ -1659,55 +1734,49 @@
     </row>
     <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35">
+        <v>17</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B35" t="s">
-        <v>30</v>
-      </c>
       <c r="C35" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D35">
-        <v>10</v>
-      </c>
-      <c r="E35" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>24</v>
-      </c>
-      <c r="B36" t="s">
-        <v>31</v>
+        <v>21</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D37">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E37" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -1715,21 +1784,27 @@
     </row>
     <row r="39" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D39">
+        <v>14</v>
+      </c>
+      <c r="E39" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -1737,145 +1812,141 @@
     </row>
     <row r="41" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D41">
-        <v>12</v>
-      </c>
-      <c r="E41" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="42" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D42">
-        <v>10</v>
-      </c>
-      <c r="E42" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D43">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A44">
+        <v>39</v>
+      </c>
+      <c r="B44" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D44">
+        <v>10</v>
+      </c>
+      <c r="E44" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>41</v>
+      </c>
+      <c r="B45" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45"/>
+      <c r="E45"/>
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
+      <c r="L45" s="17"/>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
+      <c r="O45" s="17"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="17"/>
+      <c r="R45" s="17"/>
+      <c r="S45" s="17"/>
+      <c r="T45" s="17"/>
+      <c r="U45" s="17"/>
+      <c r="V45" s="17"/>
+      <c r="W45" s="17"/>
+      <c r="X45" s="17"/>
+      <c r="Y45" s="17"/>
+      <c r="Z45" s="17"/>
+      <c r="AA45" s="17"/>
+      <c r="AB45" s="17"/>
+      <c r="AC45" s="17"/>
+      <c r="AD45" s="17"/>
+      <c r="AE45" s="17"/>
+    </row>
+    <row r="46" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46">
         <v>43</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B46" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44">
+      <c r="C46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46">
         <v>17</v>
       </c>
-      <c r="E44" t="s">
+      <c r="E46" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="45" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="10">
-        <v>44</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D45" s="10">
-        <v>11</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
-      <c r="K45" s="18"/>
-      <c r="L45" s="18"/>
-      <c r="M45" s="18"/>
-      <c r="N45" s="18"/>
-      <c r="O45" s="18"/>
-      <c r="P45" s="18"/>
-      <c r="Q45" s="18"/>
-      <c r="R45" s="18"/>
-      <c r="S45" s="18"/>
-      <c r="T45" s="18"/>
-      <c r="U45" s="18"/>
-      <c r="V45" s="18"/>
-      <c r="W45" s="18"/>
-      <c r="X45" s="18"/>
-      <c r="Y45" s="18"/>
-      <c r="Z45" s="18"/>
-      <c r="AA45" s="18"/>
-      <c r="AB45" s="18"/>
-      <c r="AC45" s="18"/>
-      <c r="AD45" s="18"/>
-      <c r="AE45" s="18"/>
-    </row>
-    <row r="46" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="10">
-        <v>45</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="D46" s="10">
-        <v>11</v>
-      </c>
-      <c r="E46" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="I46" s="18"/>
-      <c r="J46" s="18"/>
-      <c r="K46" s="18"/>
-      <c r="L46" s="18"/>
-      <c r="M46" s="18"/>
-      <c r="N46" s="18"/>
-      <c r="O46" s="18"/>
-      <c r="P46" s="18"/>
-      <c r="Q46" s="18"/>
-      <c r="R46" s="18"/>
-      <c r="S46" s="18"/>
-      <c r="T46" s="18"/>
-      <c r="U46" s="18"/>
-      <c r="V46" s="18"/>
-      <c r="W46" s="18"/>
-      <c r="X46" s="18"/>
-      <c r="Y46" s="18"/>
-      <c r="Z46" s="18"/>
-      <c r="AA46" s="18"/>
-      <c r="AB46" s="18"/>
-      <c r="AC46" s="18"/>
-      <c r="AD46" s="18"/>
-      <c r="AE46" s="18"/>
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17"/>
+      <c r="O46" s="17"/>
+      <c r="P46" s="17"/>
+      <c r="Q46" s="17"/>
+      <c r="R46" s="17"/>
+      <c r="S46" s="17"/>
+      <c r="T46" s="17"/>
+      <c r="U46" s="17"/>
+      <c r="V46" s="17"/>
+      <c r="W46" s="17"/>
+      <c r="X46" s="17"/>
+      <c r="Y46" s="17"/>
+      <c r="Z46" s="17"/>
+      <c r="AA46" s="17"/>
+      <c r="AB46" s="17"/>
+      <c r="AC46" s="17"/>
+      <c r="AD46" s="17"/>
+      <c r="AE46" s="17"/>
     </row>
     <row r="47" spans="1:31" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="10">

--- a/2026-2027-IT.xlsx
+++ b/2026-2027-IT.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8196" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="ИТ_5" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="110">
   <si>
     <t>#</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>Платформа с онлайн курсами</t>
+  </si>
+  <si>
+    <t>Серивис мониторинга и агрегации аномалий в отзывах о товарах/услугах с определением эмоциональной окраски</t>
   </si>
 </sst>
 </file>
@@ -675,7 +678,7 @@
     <col min="5" max="5" width="39.88671875" customWidth="1"/>
     <col min="6" max="6" width="22.44140625" customWidth="1"/>
     <col min="7" max="7" width="22.88671875" customWidth="1"/>
-    <col min="8" max="8" width="90.5546875" customWidth="1"/>
+    <col min="8" max="8" width="106.44140625" customWidth="1"/>
     <col min="9" max="9" width="20.44140625" style="17" customWidth="1"/>
     <col min="10" max="18" width="22.44140625" style="17" customWidth="1"/>
     <col min="19" max="19" width="33.21875" style="17" customWidth="1"/>
@@ -1501,6 +1504,9 @@
       <c r="G24">
         <v>9</v>
       </c>
+      <c r="H24" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25">
@@ -1521,6 +1527,9 @@
       <c r="G25">
         <v>9</v>
       </c>
+      <c r="H25" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26">
@@ -1540,6 +1549,9 @@
       </c>
       <c r="G26">
         <v>9</v>
+      </c>
+      <c r="H26" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
@@ -2075,330 +2087,351 @@
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
+      <c r="E2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
-      </c>
-      <c r="H4" s="9">
-        <v>6</v>
+        <v>81</v>
+      </c>
+      <c r="G4" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>83</v>
-      </c>
-      <c r="I5" s="9">
+        <v>81</v>
+      </c>
+      <c r="G5" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6">
         <v>10</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
+      <c r="E6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H7" s="9">
-        <v>6</v>
+        <v>85</v>
+      </c>
+      <c r="G7" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8">
         <v>12</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8">
-        <v>7</v>
-      </c>
       <c r="E8" t="s">
-        <v>83</v>
-      </c>
-      <c r="I8" s="9">
-        <v>2</v>
+        <v>89</v>
+      </c>
+      <c r="G8" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D9">
-        <v>3</v>
-      </c>
-      <c r="E9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H9" s="12">
-        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D10">
-        <v>4</v>
-      </c>
-      <c r="E10" t="s">
-        <v>80</v>
-      </c>
-      <c r="H10" s="12">
-        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" s="12">
-        <v>3</v>
+        <v>93</v>
+      </c>
+      <c r="H11" s="9">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E12" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="9">
+        <v>83</v>
+      </c>
+      <c r="I12" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H14" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D15">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
-      </c>
-      <c r="H15" s="9">
-        <v>5</v>
+        <v>83</v>
+      </c>
+      <c r="I15" s="9">
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" t="s">
+        <v>79</v>
+      </c>
+      <c r="H16" s="12">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="9">
-        <v>1</v>
+        <v>80</v>
+      </c>
+      <c r="H17" s="12">
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="12">
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D19">
+        <v>4</v>
+      </c>
+      <c r="E19" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="9">
         <v>2</v>
-      </c>
-      <c r="E19" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" s="9">
-        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="8" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>77</v>
-      </c>
+      <c r="D20"/>
+      <c r="E20"/>
       <c r="F20" s="9"/>
-      <c r="G20" s="9">
-        <v>1</v>
-      </c>
+      <c r="G20" s="9"/>
       <c r="H20" s="9"/>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
@@ -2407,214 +2440,214 @@
     </row>
     <row r="21" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="H21" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="D22">
+        <v>15</v>
+      </c>
+      <c r="E22" t="s">
+        <v>92</v>
+      </c>
+      <c r="H22" s="9">
+        <v>5</v>
+      </c>
     </row>
     <row r="23" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>28</v>
+        <v>15</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23">
-        <v>14</v>
-      </c>
-      <c r="E23" t="s">
-        <v>91</v>
-      </c>
-      <c r="I23" s="9">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24">
+        <v>17</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>30</v>
-      </c>
       <c r="C24" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24">
-        <v>10</v>
-      </c>
-      <c r="E24" t="s">
-        <v>85</v>
-      </c>
-      <c r="G24" s="9">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25">
+        <v>18</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
       <c r="C25" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
+        <v>20</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>81</v>
-      </c>
-      <c r="G26" s="9">
-        <v>2</v>
+        <v>78</v>
+      </c>
+      <c r="H26" s="9">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27" t="s">
-        <v>33</v>
+        <v>21</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27">
-        <v>9</v>
-      </c>
-      <c r="E27" t="s">
-        <v>88</v>
-      </c>
-      <c r="I27" s="9">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I28" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D29">
-        <v>14</v>
-      </c>
-      <c r="E29" t="s">
-        <v>91</v>
-      </c>
-      <c r="I29" s="9">
-        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D30">
+        <v>9</v>
+      </c>
+      <c r="E30" t="s">
+        <v>88</v>
+      </c>
+      <c r="I30" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D31">
+        <v>9</v>
+      </c>
+      <c r="E31" t="s">
+        <v>88</v>
+      </c>
+      <c r="I31" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D32">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E32" t="s">
-        <v>90</v>
-      </c>
-      <c r="H32" s="9">
-        <v>4</v>
+        <v>91</v>
+      </c>
+      <c r="I32" s="9">
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -2622,41 +2655,41 @@
     </row>
     <row r="34" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D34">
-        <v>5</v>
-      </c>
-      <c r="E34" t="s">
-        <v>81</v>
-      </c>
-      <c r="G34" s="9">
-        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="D35">
+        <v>13</v>
+      </c>
+      <c r="E35" t="s">
+        <v>90</v>
+      </c>
+      <c r="H35" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -2664,82 +2697,64 @@
     </row>
     <row r="37" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D37">
-        <v>12</v>
-      </c>
-      <c r="E37" t="s">
-        <v>89</v>
-      </c>
-      <c r="G37" s="9">
-        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D38">
-        <v>8</v>
-      </c>
-      <c r="E38" t="s">
-        <v>84</v>
-      </c>
-      <c r="I38" s="9">
-        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D39">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E39" t="s">
-        <v>90</v>
-      </c>
-      <c r="H39" s="9">
-        <v>4</v>
+        <v>84</v>
+      </c>
+      <c r="I39" s="9">
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D40">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E40" t="s">
-        <v>85</v>
-      </c>
-      <c r="G40" s="9">
-        <v>3</v>
+        <v>90</v>
+      </c>
+      <c r="H40" s="9">
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2904,7 +2919,7 @@
   </sheetData>
   <autoFilter ref="A1:K1">
     <sortState ref="A2:K47">
-      <sortCondition ref="A1"/>
+      <sortCondition ref="G1"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
